--- a/out/Attention-MambaAMT_repeat_1_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.854026995542006</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9612393007297437</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001356111947484314</v>
+        <v>-0.0001691554525765823</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1557912162351249</v>
+        <v>-0.194327125711051</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.854026995542006</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9612393007297437</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9612393007297437</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1944962811636276</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1560444761750703</v>
+        <v>-0.1946384352563177</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.42303809433131</v>
+        <v>0.5111534863075249</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6908439611197901</v>
+        <v>0.8286504852491278</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0301413754017528</v>
+        <v>0.03641957857970976</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3274100180553887</v>
+        <v>0.3895157688221172</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05285770265168933</v>
+        <v>0.06386753190944916</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4029739890801254</v>
+        <v>0.4808192837446879</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.064215554490124</v>
+        <v>0.0775918203608528</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4785429901189536</v>
+        <v>0.57212905886361</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01699304465147494</v>
+        <v>0.02053257473279303</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9612393007297437</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4482312446833858</v>
+        <v>0.5355036541393285</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009440134334233633</v>
+        <v>0.01140767193122314</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.450102696390254</v>
+        <v>0.537765949401522</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01983609960365269</v>
+        <v>0.02396727206053088</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4803461893691204</v>
+        <v>0.5743081143819687</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007789469846088103</v>
+        <v>0.009413519576293846</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4760731505167803</v>
+        <v>0.5691461898919966</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005545841264987817</v>
+        <v>0.006701547805553956</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4793726299736141</v>
+        <v>0.57313356758849</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002179846938942562</v>
+        <v>0.002634740490555836</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4781817949970793</v>
+        <v>0.5716959137122088</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001235837599442623</v>
+        <v>0.001493253598333204</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4784709914471626</v>
+        <v>0.5720463259633398</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004670964307340522</v>
+        <v>0.0005657434461113168</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4781695299199112</v>
+        <v>0.571682994039183</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002162930491266506</v>
+        <v>0.0002625333877501299</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4781346102789359</v>
+        <v>0.5716418378905084</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.653985472975141e-05</v>
+        <v>9.349368591118489e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.478070109422049</v>
+        <v>0.5715649655683283</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.884928758295011e-05</v>
+        <v>2.409613085119914e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4780316678108801</v>
+        <v>0.5715195703011423</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.478026649194829</v>
+        <v>0.5715145479618812</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4780225944019934</v>
+        <v>0.5715106753340242</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>5.776969076452056e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4780199769985746</v>
+        <v>0.5715086071395206</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4780144597565849</v>
+        <v>0.5715030154795123</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9612393007297437</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4780081357625769</v>
+        <v>0.5714966914855044</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4780027679739985</v>
+        <v>0.571491323696926</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9612393007297437</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4780028047224902</v>
+        <v>0.5714913604454177</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9612393007297437</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4780029149679658</v>
+        <v>0.5714914706908932</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.561239300729744</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4780029884649494</v>
+        <v>0.5714915441878768</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4780031722074086</v>
+        <v>0.571491727930336</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.478004715644065</v>
+        <v>0.5714932713669925</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4780061855837381</v>
+        <v>0.5714947413066656</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4780074350324601</v>
+        <v>0.5714959907553876</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4780087947266575</v>
+        <v>0.5714973504495849</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4780065898171482</v>
+        <v>0.5714951455400756</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4780061855837381</v>
+        <v>0.5714947413066656</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.5714938960913536</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4780058915958034</v>
+        <v>0.5714944473187309</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.478005560859377</v>
+        <v>0.5714941165823044</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4780052668714426</v>
+        <v>0.57149382259437</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.5714938960913536</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4780048993865242</v>
+        <v>0.5714934551094517</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4780047891410487</v>
+        <v>0.5714933448639761</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.478004752392557</v>
+        <v>0.5714933081154844</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4780048993865242</v>
+        <v>0.5714934551094517</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4780044216561306</v>
+        <v>0.571492977379058</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4780053771169179</v>
+        <v>0.5714939328398453</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.5714938960913536</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4780050096319998</v>
+        <v>0.5714935653549272</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4780054506139017</v>
+        <v>0.5714940063368291</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4780048258895406</v>
+        <v>0.5714933816124681</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4780046421470814</v>
+        <v>0.5714931978700089</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4780042379136714</v>
+        <v>0.5714927936365989</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4780033926983595</v>
+        <v>0.5714919484212869</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4780033559498678</v>
+        <v>0.5714919116727952</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9612393007297437</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.478003502943835</v>
+        <v>0.5714920586667624</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4780034294468514</v>
+        <v>0.5714919851697788</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.478003502943835</v>
+        <v>0.5714920586667624</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4780035396923269</v>
+        <v>0.5714920954152544</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4780034294468514</v>
+        <v>0.5714919851697788</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4780038704287533</v>
+        <v>0.5714924261516807</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4780037601832778</v>
+        <v>0.5714923159062052</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4780037234347859</v>
+        <v>0.5714922791577133</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4780036499378022</v>
+        <v>0.5714922056607297</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4780036131893106</v>
+        <v>0.571492168912238</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4780033926983595</v>
+        <v>0.5714919484212869</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4780033192013758</v>
+        <v>0.5714918749243033</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4780032457043922</v>
+        <v>0.5714918014273197</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.561239300729744</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4780032824528841</v>
+        <v>0.5714918381758116</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4780031722074086</v>
+        <v>0.571491727930336</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4780032824528841</v>
+        <v>0.5714918381758116</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4780035764408186</v>
+        <v>0.5714921321637461</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.1403843525070613</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.9056185112288041</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.9056185112288041</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.254026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001356111947484314</v>
+        <v>-0.0001233764843078097</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1557912162351249</v>
+        <v>-0.1417358838315298</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1559268274298734</v>
+        <v>-0.1418592603158376</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1560444761750703</v>
+        <v>-0.1419672588233319</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.42303809433131</v>
+        <v>0.388337780557553</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6908439611197901</v>
+        <v>0.6354544395297729</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0301413754017528</v>
+        <v>0.02766902191717459</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3274100180553887</v>
+        <v>0.3018312520653636</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05285770265168933</v>
+        <v>0.04852203702277105</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4029739890801254</v>
+        <v>0.3711970703986106</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.064215554490124</v>
+        <v>0.05894823278903567</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4785429901189536</v>
+        <v>0.4405675062050647</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01699304465147494</v>
+        <v>0.01559934436863985</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4482312446833858</v>
+        <v>0.4127420764988058</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009440134334233633</v>
+        <v>0.008665299464787082</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.561239300729744</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.450102696390254</v>
+        <v>0.4144595958540679</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01983609960365269</v>
+        <v>0.0182089015005332</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4803461893691204</v>
+        <v>0.442222149767784</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007789469846088103</v>
+        <v>0.00715002297245005</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4760731505167803</v>
+        <v>0.4382992274296144</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005545841264987817</v>
+        <v>0.005090458389302052</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4793726299736141</v>
+        <v>0.4413276544457465</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002179846938942562</v>
+        <v>0.002000605300694944</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4781817949970793</v>
+        <v>0.4402340734834398</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001235837599442623</v>
+        <v>0.001134104330419998</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4784709914471626</v>
+        <v>0.4404991494792304</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004670964307340522</v>
+        <v>0.0004283422461215553</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9612393007297437</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4781695299199112</v>
+        <v>0.4402219941793345</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002162930491266506</v>
+        <v>0.0001986776820319919</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4781346102789359</v>
+        <v>0.4401895238478002</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.653985472975141e-05</v>
+        <v>6.927392708056564e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.478070109422049</v>
+        <v>0.4401300310595331</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.884928758295011e-05</v>
+        <v>1.69413445763141e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4780316678108801</v>
+        <v>0.4400942383183434</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.478026649194829</v>
+        <v>0.4400892211915765</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4780225944019934</v>
+        <v>0.4400850936904976</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4780199769985746</v>
+        <v>0.4400822925446199</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4780144597565849</v>
+        <v>0.4400768487996136</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4780081357625769</v>
+        <v>0.4400708560661832</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4780027679739985</v>
+        <v>0.4400654882776048</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4780028047224902</v>
+        <v>0.4400655250260965</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4780029149679658</v>
+        <v>0.4400656352715721</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.561239300729744</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4780029884649494</v>
+        <v>0.4400657087685557</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4780031722074086</v>
+        <v>0.4400658925110148</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.478004715644065</v>
+        <v>0.4400674359476713</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4780061855837381</v>
+        <v>0.4400689058873444</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4780074350324601</v>
+        <v>0.4400701553360664</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4780087947266575</v>
+        <v>0.4400715150302637</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4780065898171482</v>
+        <v>0.4400693101207544</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4780061855837381</v>
+        <v>0.4400689058873444</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.4400680606720324</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4780058915958034</v>
+        <v>0.4400686118994097</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.478005560859377</v>
+        <v>0.4400682811629833</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9612393007297437</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4780052668714426</v>
+        <v>0.4400679871750488</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.4400680606720324</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4780048993865242</v>
+        <v>0.4400676196901305</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4780047891410487</v>
+        <v>0.4400675094446549</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.478004752392557</v>
+        <v>0.4400674726961633</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4780048993865242</v>
+        <v>0.4400676196901305</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4780044216561306</v>
+        <v>0.4400671419597368</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4780053771169179</v>
+        <v>0.4400680974205241</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4780053403684262</v>
+        <v>0.4400680606720324</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4780050096319998</v>
+        <v>0.440067729935606</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4780054506139017</v>
+        <v>0.4400681709175079</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4780048258895406</v>
+        <v>0.4400675461931469</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4780046421470814</v>
+        <v>0.4400673624506877</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4780042379136714</v>
+        <v>0.4400669582172776</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4780033926983595</v>
+        <v>0.4400661130019657</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4780033559498678</v>
+        <v>0.440066076253474</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.478003502943835</v>
+        <v>0.4400662232474412</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4780034294468514</v>
+        <v>0.4400661497504576</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.478003502943835</v>
+        <v>0.4400662232474412</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4780035396923269</v>
+        <v>0.4400662599959331</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4780034294468514</v>
+        <v>0.4400661497504576</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4780038704287533</v>
+        <v>0.4400665907323595</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4780037601832778</v>
+        <v>0.440066480486884</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4780037234347859</v>
+        <v>0.4400664437383921</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4780036499378022</v>
+        <v>0.4400663702414085</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4780036131893106</v>
+        <v>0.4400663334929168</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4780033926983595</v>
+        <v>0.4400661130019657</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.254026995542006</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4780033192013758</v>
+        <v>0.4400660395049821</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4780032457043922</v>
+        <v>0.4400659660079985</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4780032824528841</v>
+        <v>0.4400660027564904</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4780031722074086</v>
+        <v>0.4400658925110148</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4780032824528841</v>
+        <v>0.4400660027564904</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4780035764408186</v>
+        <v>0.4400662967444248</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01794656366109848</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1403843525070613</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0005712863057851791</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01474672369658947</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.06131687015295029</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01725101657211781</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.381360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005520596168935299</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.01024836394935846</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.006295778788626194</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01326264906674623</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0053011579439044</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0154004218056798</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.007364607416093349</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01552120689302683</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.00779560673981905</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.004489057697355747</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005827993154525757</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01302172709256411</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01034532953053713</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9056185112288041</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01084296870976686</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9056185112288041</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01331518311053514</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.008406450040638447</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01865407824516296</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01151703763753176</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.01847941428422928</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.002422879450023174</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.01819797232747078</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01058883126825094</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01911264285445213</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0184846967458725</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.007103958167135715</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.003604387398809195</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.381360367066853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01344495639204979</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.381360367066853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.02059751749038696</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.01825371384620667</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0007479004561901093</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.02250475063920021</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.009611711837351322</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.01499238889664412</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.01419939566403627</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01389327924698591</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.01559225376695395</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0162084624171257</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.381360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01697505079209805</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.04957101121544838</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001233764843078097</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1417358838315298</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.05439139530062675</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.008497657254338264</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.02138258516788483</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.007866687141358852</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.003320473246276379</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01529135275632143</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0001577632501721382</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001435036770999432</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.003299904055893421</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.005682448856532574</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.004456697963178158</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01001298055052757</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02366791479289532</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1418592603158376</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.005106338299810886</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1419672588233319</v>
+        <v>-0.1413152098439792</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.388337780557553</v>
+        <v>0.3866971705496043</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03469131514430046</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6354544395297729</v>
+        <v>0.6328216039830502</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02766902191717459</v>
+        <v>0.02755209221229843</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0101844547316432</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.381360367066853</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3018312520653636</v>
+        <v>0.3006083131520255</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04852203702277105</v>
+        <v>0.04831698216083748</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0002305610105395317</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3711970703986106</v>
+        <v>0.3696809904884391</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05894823278903567</v>
+        <v>0.05869942713510714</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.02129669673740864</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4405675062050647</v>
+        <v>0.4387582652113344</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01559934436863985</v>
+        <v>0.01553333914567821</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01768359914422035</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4127420764988058</v>
+        <v>0.4110505727412286</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008665299464787082</v>
+        <v>0.008628612207711016</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.00379350408911705</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4144595958540679</v>
+        <v>0.4127608036328733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0182089015005332</v>
+        <v>0.01813185613580216</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03164800256490707</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.442222149767784</v>
+        <v>0.440405888840853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00715002297245005</v>
+        <v>0.007119746131842187</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01527740526944399</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4382992274296144</v>
+        <v>0.4364995439891501</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005090458389302052</v>
+        <v>0.005069759167679973</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01354220882058144</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4413276544457465</v>
+        <v>0.43951513596091</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002000605300694944</v>
+        <v>0.00199245795350187</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.005786346271634102</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4402340734834398</v>
+        <v>0.4384263431205321</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001134104330419998</v>
+        <v>0.00112793867775196</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0106404572725296</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4404991494792304</v>
+        <v>0.4386901410130672</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004283422461215553</v>
+        <v>0.0004271678768908736</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.004571433179080486</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4402219941793345</v>
+        <v>0.4384140897504338</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001986776820319919</v>
+        <v>0.0001975767215885757</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0179455541074276</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4401895238478002</v>
+        <v>0.438381767907178</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.02357478812336922</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4401300310595331</v>
+        <v>0.4383225691068454</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.008965574204921722</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4400942383183434</v>
+        <v>0.4382871071020824</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.02519986033439636</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4400892211915765</v>
+        <v>0.4382820899753154</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.004522371105849743</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4400850936904976</v>
+        <v>0.4382779265144847</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01376565918326378</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4400822925446199</v>
+        <v>0.438275125368607</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.02628535777330399</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4400768487996136</v>
+        <v>0.4382696816236006</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02101698145270348</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.181360367066853</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4400708560661832</v>
+        <v>0.4382636888901703</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002379813231527805</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.181360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4400654882776048</v>
+        <v>0.4382583211015919</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.03239321336150169</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.181360367066853</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4400655250260965</v>
+        <v>0.4382583578500836</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.006531521212309599</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4400656352715721</v>
+        <v>0.4382584680955592</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01519621722400188</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4400657087685557</v>
+        <v>0.4382585415925428</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01346016768366098</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4400658925110148</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.02517814189195633</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4400674359476713</v>
+        <v>0.4382602687716584</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0004037348553538322</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4400689058873444</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02670324221253395</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4400701553360664</v>
+        <v>0.4382629881600535</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.08301077038049698</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4400715150302637</v>
+        <v>0.4382643478542508</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001818859949707985</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4400693101207544</v>
+        <v>0.4382621429447415</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.04258378222584724</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.024849806214682</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4400689058873444</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0001004608348011971</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4400680606720324</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01216182857751846</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4400686118994097</v>
+        <v>0.4382614447233968</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.009575864300131798</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4400682811629833</v>
+        <v>0.4382611139869704</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002295964397490025</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4400679871750488</v>
+        <v>0.4382608199990359</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0215313732624054</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4400680606720324</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.006500833667814732</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4400676196901305</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.002366657368838787</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4400675094446549</v>
+        <v>0.438260342268642</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.001515106298029423</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4400674726961633</v>
+        <v>0.4382603055201503</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02962282299995422</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.181360367066853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4400676196901305</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01011641230434179</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4400671419597368</v>
+        <v>0.4382599747837239</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02982740104198456</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.381360367066853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4400680974205241</v>
+        <v>0.4382609302445112</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003974857740104198</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4400680606720324</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004324936307966709</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.440067729935606</v>
+        <v>0.4382605627595931</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.02138441056013107</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4400681709175079</v>
+        <v>0.4382610037414951</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0117894196882844</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4400675461931469</v>
+        <v>0.4382603790171339</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01364437025040388</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.024849806214682</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4400673624506877</v>
+        <v>0.4382601952746748</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.02770032361149788</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.381360367066853</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4400669582172776</v>
+        <v>0.4382597910412648</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01049843523651361</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4400661130019657</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01468884292989969</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.440066076253474</v>
+        <v>0.4382589090774611</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.008730543777346611</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4400662232474412</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004713370464742184</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4400661497504576</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01307113561779261</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4400662232474412</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006772276945412159</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4400662599959331</v>
+        <v>0.4382590928199203</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01945687085390091</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4400661497504576</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001183400861918926</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4400665907323595</v>
+        <v>0.4382594235563467</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.006877169944345951</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.440066480486884</v>
+        <v>0.4382593133108711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00107892882078886</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4400664437383921</v>
+        <v>0.4382592765623792</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.003767360001802444</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4400663702414085</v>
+        <v>0.4382592030653956</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.002937343902885914</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4400663334929168</v>
+        <v>0.4382591663169039</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.003137617837637663</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4400661130019657</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.005382114090025425</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4400660395049821</v>
+        <v>0.4382588723289692</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001940409187227488</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4400659660079985</v>
+        <v>0.4382587988319855</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001734111458063126</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4400660027564904</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0009762672707438469</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4400658925110148</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.007394318468868732</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4400660027564904</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0154110761359334</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4400662967444248</v>
+        <v>0.438259129568412</v>
       </c>
     </row>
   </sheetData>
